--- a/data/trans_orig/CoTrAQ-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52865</t>
+          <t>53856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47309</t>
+          <t>48216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63916</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82608</t>
+          <t>82134</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>108194</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48385</t>
+          <t>47080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78436</t>
+          <t>76996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36909</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63003</t>
+          <t>63591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91135</t>
+          <t>89245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129757</t>
+          <t>129215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71813</t>
+          <t>72852</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55009</t>
+          <t>54952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82094</t>
+          <t>80845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120591</t>
+          <t>119694</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>235705</t>
+          <t>236429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270918</t>
+          <t>273568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158475</t>
+          <t>157375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>188625</t>
+          <t>189129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>406508</t>
+          <t>405724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>455135</t>
+          <t>454009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>42365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72881</t>
+          <t>71267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34654</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>59651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83248</t>
+          <t>85809</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124942</t>
+          <t>124709</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>46005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75547</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44821</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73568</t>
+          <t>71563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97833</t>
+          <t>97074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137148</t>
+          <t>135973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275856</t>
+          <t>275223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311550</t>
+          <t>314423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154852</t>
+          <t>155205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187740</t>
+          <t>187115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441168</t>
+          <t>443677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>491353</t>
+          <t>489812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52742</t>
+          <t>52950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58094</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93451</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68464</t>
+          <t>67037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46248</t>
+          <t>46129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104577</t>
+          <t>107118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>254185</t>
+          <t>253576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>290333</t>
+          <t>288073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126482</t>
+          <t>124498</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156222</t>
+          <t>154921</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>389937</t>
+          <t>389329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>435170</t>
+          <t>436203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37529</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31540</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42049</t>
+          <t>42210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105140</t>
+          <t>103930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149829</t>
+          <t>148471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176219</t>
+          <t>176951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3124,97 +3124,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>157107</t>
+          <t>159502</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>210326</t>
+          <t>214712</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>130100</t>
+          <t>132265</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>178100</t>
+          <t>181322</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>303929</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>377817</t>
+          <t>375033</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>188932</t>
+          <t>190051</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>247193</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>135744</t>
+          <t>134966</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>338714</t>
+          <t>337359</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>410745</t>
+          <t>411728</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>944619</t>
+          <t>944768</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1016884</t>
+          <t>1016177</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>562098</t>
+          <t>563741</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>620915</t>
+          <t>621024</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1525136</t>
+          <t>1521554</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1613385</t>
+          <t>1616962</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>35888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34685</t>
+          <t>36383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>41424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65769</t>
+          <t>65390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25398</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44137</t>
+          <t>44039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>66228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91259</t>
+          <t>91210</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>80738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114460</t>
+          <t>114686</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68938</t>
+          <t>68574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97009</t>
+          <t>97657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157184</t>
+          <t>158750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200558</t>
+          <t>201722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>59183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88959</t>
+          <t>88901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>38817</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63522</t>
+          <t>63750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>106440</t>
+          <t>105557</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>145223</t>
+          <t>143330</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155852</t>
+          <t>156437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191705</t>
+          <t>192762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124704</t>
+          <t>124112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157563</t>
+          <t>156129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289300</t>
+          <t>289985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339651</t>
+          <t>337480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78381</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113938</t>
+          <t>116199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66716</t>
+          <t>66405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97841</t>
+          <t>98261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154779</t>
+          <t>156358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203307</t>
+          <t>203126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96486</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133415</t>
+          <t>135956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83599</t>
+          <t>85325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162060</t>
+          <t>159463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208831</t>
+          <t>207596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228492</t>
+          <t>227469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271603</t>
+          <t>271752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146992</t>
+          <t>146997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182509</t>
+          <t>183778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387680</t>
+          <t>388374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442854</t>
+          <t>444656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68123</t>
+          <t>69169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102559</t>
+          <t>103057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61024</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90750</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135537</t>
+          <t>137531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181626</t>
+          <t>184249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55080</t>
+          <t>54839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>86867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38033</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63017</t>
+          <t>62966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>99810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139461</t>
+          <t>138426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193166</t>
+          <t>190776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>232037</t>
+          <t>232441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103550</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>136176</t>
+          <t>135834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>307911</t>
+          <t>309221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>358834</t>
+          <t>357416</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>28791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52769</t>
+          <t>51153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>57784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87532</t>
+          <t>88917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40146</t>
+          <t>39523</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>38788</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71463</t>
+          <t>72412</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83312</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>110355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>34699</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>57840</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126683</t>
+          <t>125570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160724</t>
+          <t>160445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -6894,97 +6894,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -7350,97 +7350,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -7463,97 +7463,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -7576,97 +7576,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>312169</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>377952</t>
+          <t>377903</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>268682</t>
+          <t>269613</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>328058</t>
+          <t>329225</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>600016</t>
+          <t>597361</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>689283</t>
+          <t>688323</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>273836</t>
+          <t>273677</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>338540</t>
+          <t>335916</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>196384</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>249988</t>
+          <t>250339</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>486137</t>
+          <t>484041</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>564097</t>
+          <t>573467</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>736066</t>
+          <t>737475</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>812043</t>
+          <t>811516</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>484910</t>
+          <t>485112</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>549948</t>
+          <t>549827</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1239983</t>
+          <t>1244271</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1340572</t>
+          <t>1340367</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoTrAQ-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>24264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>54200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>29603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>47544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>64212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82134</t>
+          <t>81307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108194</t>
+          <t>107650</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47080</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>75482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63591</t>
+          <t>62064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89245</t>
+          <t>92462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129215</t>
+          <t>132147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72852</t>
+          <t>72533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31222</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54952</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80845</t>
+          <t>79348</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119694</t>
+          <t>116625</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236429</t>
+          <t>238342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>273568</t>
+          <t>273476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157375</t>
+          <t>158500</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189129</t>
+          <t>189162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>405724</t>
+          <t>406769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>454009</t>
+          <t>453544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42365</t>
+          <t>43358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71267</t>
+          <t>73107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>60821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85809</t>
+          <t>86037</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124709</t>
+          <t>123869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46005</t>
+          <t>45593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74814</t>
+          <t>75490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71563</t>
+          <t>72016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97074</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>137348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275223</t>
+          <t>274970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314423</t>
+          <t>311634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155205</t>
+          <t>156237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187115</t>
+          <t>186581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443677</t>
+          <t>440681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>489812</t>
+          <t>490985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47535</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52950</t>
+          <t>53650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58165</t>
+          <t>58524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>39177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67037</t>
+          <t>67790</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46129</t>
+          <t>46311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>70825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107118</t>
+          <t>105460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253576</t>
+          <t>254407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>288073</t>
+          <t>288347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124498</t>
+          <t>125504</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154921</t>
+          <t>155551</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>389329</t>
+          <t>388372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>436203</t>
+          <t>435387</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37097</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32147</t>
+          <t>32601</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42210</t>
+          <t>40652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103930</t>
+          <t>104528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126523</t>
+          <t>126332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>53986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148471</t>
+          <t>150361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176951</t>
+          <t>176949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>159502</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>214712</t>
+          <t>209965</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>132265</t>
+          <t>131060</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>181322</t>
+          <t>178080</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>304159</t>
+          <t>305181</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>375033</t>
+          <t>373668</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>190051</t>
+          <t>189788</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>247193</t>
+          <t>246228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>134966</t>
+          <t>136060</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>179078</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>333165</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>411728</t>
+          <t>411520</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>944768</t>
+          <t>945134</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1016177</t>
+          <t>1012419</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>563741</t>
+          <t>562357</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>621024</t>
+          <t>620636</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1521554</t>
+          <t>1526867</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1616962</t>
+          <t>1620120</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19220</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36383</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65390</t>
+          <t>64046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>29934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>52466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>44755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52079</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66228</t>
+          <t>65606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91210</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80738</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114686</t>
+          <t>112541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68574</t>
+          <t>68204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97657</t>
+          <t>98409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158750</t>
+          <t>158127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201722</t>
+          <t>202880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>59501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88901</t>
+          <t>89575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>39511</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63750</t>
+          <t>64883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>105557</t>
+          <t>104961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143330</t>
+          <t>144846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>157066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192762</t>
+          <t>194222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124112</t>
+          <t>125012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156129</t>
+          <t>156362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289985</t>
+          <t>290171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337480</t>
+          <t>340605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>79779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116199</t>
+          <t>113898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66405</t>
+          <t>66792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98261</t>
+          <t>97728</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>156358</t>
+          <t>154069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203126</t>
+          <t>201425</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96380</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135956</t>
+          <t>134146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55098</t>
+          <t>56693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85325</t>
+          <t>85045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159463</t>
+          <t>160315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207596</t>
+          <t>207337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227469</t>
+          <t>225906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271752</t>
+          <t>270727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>149072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183778</t>
+          <t>183438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388374</t>
+          <t>385790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>444656</t>
+          <t>442996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69169</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103057</t>
+          <t>102057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60028</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>88483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137531</t>
+          <t>136408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>184249</t>
+          <t>181870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>55470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86867</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62966</t>
+          <t>63248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99810</t>
+          <t>99823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138426</t>
+          <t>140296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190776</t>
+          <t>194720</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>232441</t>
+          <t>232904</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>103632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>135834</t>
+          <t>135101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>309221</t>
+          <t>305542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>357416</t>
+          <t>357594</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>43180</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>56989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88917</t>
+          <t>88635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39523</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38788</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>72412</t>
+          <t>71192</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84056</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110355</t>
+          <t>110130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34699</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57840</t>
+          <t>56262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125570</t>
+          <t>127172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160445</t>
+          <t>161969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>312169</t>
+          <t>310752</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>377903</t>
+          <t>377615</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>269613</t>
+          <t>271231</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>329225</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>597361</t>
+          <t>599114</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>688323</t>
+          <t>687936</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>273677</t>
+          <t>275003</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>335916</t>
+          <t>334427</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>196384</t>
+          <t>194801</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>250339</t>
+          <t>250623</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>484041</t>
+          <t>484770</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>573467</t>
+          <t>567940</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>737475</t>
+          <t>736907</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>811516</t>
+          <t>811385</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>485112</t>
+          <t>483378</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>549827</t>
+          <t>554116</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1244271</t>
+          <t>1236812</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1340367</t>
+          <t>1340746</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
